--- a/docs/programs/NAS_MAIL_SPEC.xlsx
+++ b/docs/programs/NAS_MAIL_SPEC.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Overview" sheetId="1" r:id="Rdcd20fb7570a4f77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Account_Types" sheetId="2" r:id="Rf3a99114e99541a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Roles" sheetId="3" r:id="R4446007d83f44335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Addresses" sheetId="4" r:id="R7ae855edc8524a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Flows" sheetId="5" r:id="R2ae9201fd97a48b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Security" sheetId="6" r:id="R7d187a47b9754c0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_API_Map" sheetId="7" r:id="R29a59b470fbc48a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Data_Model" sheetId="8" r:id="R228a89ac80114d78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Test_Matrix" sheetId="9" r:id="R642c09572b484a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Roadmap" sheetId="10" r:id="R0305a0ffd74a4e4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Change_Log" sheetId="11" r:id="R310205ec5cdf4b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Overview" sheetId="1" r:id="Rc0b1f90757d040ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Account_Types" sheetId="2" r:id="R557f07bf1859471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Roles" sheetId="3" r:id="R0a88f062b7524de7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Addresses" sheetId="4" r:id="Rea6ac897683d4d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Flows" sheetId="5" r:id="R87be1d168bd24a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Security" sheetId="6" r:id="R70ae141bdeaf4f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_API_Map" sheetId="7" r:id="R96de145866904a41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Data_Model" sheetId="8" r:id="R0ed0452fe0054a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Test_Matrix" sheetId="9" r:id="R85b73537136c42c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Roadmap" sheetId="10" r:id="R2055cd32b29c47e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Change_Log" sheetId="11" r:id="Rd9e06ecaa9604b68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -501,6 +501,17 @@
         <x:v>artifact-tool render/reopen/formula/mojibake scan</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="4" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>운영 배포: 25개 기존 계정을 미분류로 안전 이관, 새 가입 UI·API 반영</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="str">
+        <x:v>commit 826c502, bundle main.4f405bb2.js, SHA-256 a2518f7c...f8c5</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1431,7 +1442,7 @@
         <x:v>NAS pull/build/restart/API/UI</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>이 작업 배포 후 입력</x:v>
+        <x:v>pass: public API/site/bundle, services, PM2, 25 identity migration, signup UI; admin UI requires authenticated visual follow-up</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
